--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1301,6 +1301,120 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114846602</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57254</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stora Brotrop, aspdunge, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>566685</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6622182</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117854805</v>
+        <v>117854666</v>
       </c>
       <c r="B13" t="n">
-        <v>57691</v>
+        <v>56534</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2044,20 +2044,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103037</v>
+        <v>102118</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2065,12 +2065,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2110,27 +2114,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Asparna bakom huset.</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2286,10 +2285,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117854666</v>
+        <v>117854805</v>
       </c>
       <c r="B15" t="n">
-        <v>56534</v>
+        <v>57691</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2298,20 +2297,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102118</v>
+        <v>103037</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2319,16 +2318,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2368,22 +2363,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Asparna bakom huset.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -2035,7 +2035,7 @@
         <v>117854666</v>
       </c>
       <c r="B13" t="n">
-        <v>56534</v>
+        <v>56535</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>117855091</v>
       </c>
       <c r="B14" t="n">
-        <v>57924</v>
+        <v>57925</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>117854805</v>
       </c>
       <c r="B15" t="n">
-        <v>57691</v>
+        <v>57692</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>117855143</v>
       </c>
       <c r="B16" t="n">
-        <v>56741</v>
+        <v>56742</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -2656,14 +2656,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121169138</v>
+        <v>121169145</v>
       </c>
       <c r="B18" t="n">
-        <v>57776</v>
+        <v>57267</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2672,24 +2672,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103001</v>
+        <v>100067</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
@@ -2737,14 +2741,19 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2771,14 +2780,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121168871</v>
+        <v>121169135</v>
       </c>
       <c r="B19" t="n">
-        <v>57782</v>
+        <v>57785</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2804,12 +2813,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2849,12 +2862,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2881,14 +2899,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121168887</v>
+        <v>121169138</v>
       </c>
       <c r="B20" t="n">
-        <v>57264</v>
+        <v>57779</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2897,33 +2915,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100067</v>
+        <v>103001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2963,12 +2977,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -2656,14 +2656,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121169145</v>
+        <v>121169138</v>
       </c>
       <c r="B18" t="n">
-        <v>57267</v>
+        <v>57779</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2672,28 +2672,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100067</v>
+        <v>103001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
@@ -2741,19 +2737,14 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2780,14 +2771,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121169135</v>
+        <v>121168871</v>
       </c>
       <c r="B19" t="n">
         <v>57785</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2813,16 +2804,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2862,17 +2849,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2899,14 +2881,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121169138</v>
+        <v>121168887</v>
       </c>
       <c r="B20" t="n">
-        <v>57779</v>
+        <v>57267</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2915,29 +2897,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103001</v>
+        <v>100067</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2977,17 +2963,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -2656,10 +2656,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121169138</v>
+        <v>121168871</v>
       </c>
       <c r="B18" t="n">
-        <v>57779</v>
+        <v>57785</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2672,21 +2672,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2694,7 +2694,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2734,17 +2734,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2771,14 +2766,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121168871</v>
+        <v>121169145</v>
       </c>
       <c r="B19" t="n">
-        <v>57785</v>
+        <v>57267</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2787,29 +2782,33 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102999</v>
+        <v>100067</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2849,12 +2848,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2881,14 +2890,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121168887</v>
+        <v>121168868</v>
       </c>
       <c r="B20" t="n">
-        <v>57267</v>
+        <v>57779</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2897,33 +2906,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100067</v>
+        <v>103001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -2656,10 +2656,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121168871</v>
+        <v>121169138</v>
       </c>
       <c r="B18" t="n">
-        <v>57785</v>
+        <v>57779</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2672,21 +2672,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2694,7 +2694,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2734,12 +2734,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2890,14 +2895,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121168868</v>
+        <v>121169135</v>
       </c>
       <c r="B20" t="n">
-        <v>57779</v>
+        <v>57785</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2906,29 +2911,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2968,12 +2977,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -2656,14 +2656,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121169138</v>
+        <v>121168887</v>
       </c>
       <c r="B18" t="n">
-        <v>57779</v>
+        <v>57270</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2672,29 +2672,33 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103001</v>
+        <v>100067</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2734,17 +2738,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2771,10 +2770,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121169145</v>
+        <v>121169135</v>
       </c>
       <c r="B19" t="n">
-        <v>57267</v>
+        <v>57788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2787,26 +2786,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100067</v>
+        <v>102999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2856,19 +2855,14 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2895,14 +2889,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121169135</v>
+        <v>121168868</v>
       </c>
       <c r="B20" t="n">
-        <v>57785</v>
+        <v>57782</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2911,33 +2905,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2977,17 +2967,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -2656,14 +2656,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121168887</v>
+        <v>121169138</v>
       </c>
       <c r="B18" t="n">
-        <v>57270</v>
+        <v>57782</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2672,33 +2672,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100067</v>
+        <v>103001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2738,12 +2734,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2770,14 +2771,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121169135</v>
+        <v>121168871</v>
       </c>
       <c r="B19" t="n">
         <v>57788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2803,16 +2804,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2852,17 +2849,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2889,14 +2881,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121168868</v>
+        <v>121169145</v>
       </c>
       <c r="B20" t="n">
-        <v>57782</v>
+        <v>57270</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2905,29 +2897,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103001</v>
+        <v>100067</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2967,12 +2963,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -2656,14 +2656,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121169138</v>
+        <v>121169135</v>
       </c>
       <c r="B18" t="n">
-        <v>57782</v>
+        <v>57789</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2672,24 +2672,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
@@ -2771,14 +2775,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121168871</v>
+        <v>121169145</v>
       </c>
       <c r="B19" t="n">
-        <v>57788</v>
+        <v>57271</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2787,29 +2791,33 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102999</v>
+        <v>100067</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2849,12 +2857,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2881,14 +2899,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121169145</v>
+        <v>121169138</v>
       </c>
       <c r="B20" t="n">
-        <v>57270</v>
+        <v>57783</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2897,28 +2915,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100067</v>
+        <v>103001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
@@ -2966,19 +2980,14 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flock med ca 50 björktrastar och några rödvingetrastar</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3012,6 +3012,130 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122618558</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57274</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stora brotorp, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>566730</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6622185</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3017,11 +3017,11 @@
         <v>122618558</v>
       </c>
       <c r="B21" t="n">
-        <v>57274</v>
+        <v>57275</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3017,7 +3017,7 @@
         <v>122618558</v>
       </c>
       <c r="B21" t="n">
-        <v>57275</v>
+        <v>57369</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3136,6 +3136,135 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123281331</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57657</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stora Brotorp, norra hygget, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>566672</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6622276</v>
+      </c>
+      <c r="S22" t="n">
+        <v>100</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Sjöng några strofer och flög sedan norrut/sträckte vidare mot NO</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3145,7 +3145,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3141,7 +3141,7 @@
         <v>123281331</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3141,7 +3141,7 @@
         <v>123281331</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3264,6 +3264,130 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>85795993</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57484</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stora Brotorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>566720</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6622026</v>
+      </c>
+      <c r="S23" t="n">
+        <v>75</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-04-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-04-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3141,7 +3141,7 @@
         <v>123281331</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57669</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>85795993</v>
       </c>
       <c r="B23" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3141,7 +3141,7 @@
         <v>123281331</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>85795993</v>
       </c>
       <c r="B23" t="n">
-        <v>57487</v>
+        <v>57488</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3389,6 +3389,130 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124066382</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56943</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stora Brotorp, NÖ hygge, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>566801</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6622227</v>
+      </c>
+      <c r="S24" t="n">
+        <v>100</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3391,7 +3391,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124066382</v>
+        <v>124171828</v>
       </c>
       <c r="B24" t="n">
         <v>56943</v>
@@ -3433,7 +3433,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3473,22 +3473,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,6 +3637,120 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125165926</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58016</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stora Brotorp, NÖ hygge, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>566801</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6622227</v>
+      </c>
+      <c r="S26" t="n">
+        <v>100</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3646,7 +3646,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3751,6 +3751,130 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125254455</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stora Brotorp, västra aspdunge, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>566668</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6621990</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3760,7 +3760,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3518,7 +3518,7 @@
         <v>124506365</v>
       </c>
       <c r="B25" t="n">
-        <v>57510</v>
+        <v>57624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>125165926</v>
       </c>
       <c r="B26" t="n">
-        <v>58016</v>
+        <v>58134</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>125254455</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3642,12 +3642,7 @@
         <v>125165926</v>
       </c>
       <c r="B26" t="n">
-        <v>58134</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58153</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3756,12 +3751,7 @@
         <v>125254455</v>
       </c>
       <c r="B27" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3865,6 +3865,125 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126155160</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57824</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stora Brotorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>566720</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6622026</v>
+      </c>
+      <c r="S28" t="n">
+        <v>75</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Inger-Marie Carlsen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3870,7 +3870,7 @@
         <v>126155160</v>
       </c>
       <c r="B28" t="n">
-        <v>57824</v>
+        <v>57825</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3870,7 +3870,7 @@
         <v>126155160</v>
       </c>
       <c r="B28" t="n">
-        <v>57825</v>
+        <v>57829</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 12116-2023 artfynd.xlsx
+++ b/artfynd/A 12116-2023 artfynd.xlsx
@@ -3870,7 +3870,7 @@
         <v>126155160</v>
       </c>
       <c r="B28" t="n">
-        <v>57829</v>
+        <v>57830</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
